--- a/datos/LISTA1.xlsx
+++ b/datos/LISTA1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-6 LAB2\Documents\OTM-106 David\OTM106-2025\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67295FB-AD75-4298-8DCE-28656D4A9D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4976656B-831B-4593-AC64-1285477F3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2C2EDEAE-2E2E-4BC6-BAF0-416FF216200E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>Número</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>Promedio edad</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -413,14 +419,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949A2EF5-6C3A-4212-9666-0025893AA56B}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,8 +442,14 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -457,8 +469,16 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <f>IF(F2="M",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>IF(F2="F",1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -478,8 +498,16 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <f t="shared" ref="G3:G6" si="1">IF(F3="M",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H6" si="2">IF(F3="F",1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -499,8 +527,16 @@
       <c r="F4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -520,8 +556,16 @@
       <c r="F5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -541,9 +585,50 @@
       <c r="F6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C7" s="1"/>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <f>AVERAGE(E2:E6)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <f>SUM(G2:G6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <f>SUM(H2:H6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <f>SUM(E8:E9)</f>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
